--- a/samples/ss_tjati_ungaran3_ingest.xlsx
+++ b/samples/ss_tjati_ungaran3_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,19 +692,16 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>1 IBT (unit 3)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -730,7 +717,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -759,31 +745,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -830,15 +806,11 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -854,7 +826,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -901,15 +872,11 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -925,7 +892,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -954,19 +920,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -982,7 +940,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1011,31 +968,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1064,31 +1011,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1117,19 +1054,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1145,7 +1074,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1174,31 +1102,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1227,31 +1145,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1280,31 +1188,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1333,31 +1231,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1386,19 +1274,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1414,7 +1294,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1443,31 +1322,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1496,31 +1365,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1549,31 +1408,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1602,31 +1451,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1655,31 +1494,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1708,19 +1537,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1736,7 +1557,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1765,31 +1585,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1818,19 +1628,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1846,7 +1648,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1875,35 +1676,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>Bus 1</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1932,35 +1724,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>KTT SBGAN</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1989,19 +1772,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2017,7 +1792,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2046,31 +1820,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2099,35 +1863,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>KTT SINDO</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2156,19 +1911,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2184,7 +1931,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2213,31 +1959,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2266,19 +2002,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2294,7 +2022,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2323,19 +2050,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2351,7 +2070,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2380,31 +2098,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2433,31 +2141,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2486,19 +2184,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2514,7 +2204,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2543,19 +2232,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2571,7 +2252,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2600,17 +2280,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>batas ke Subsistem Boyolali 1,2</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2626,13 +2300,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2661,17 +2333,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>batas ke Subsistem Kesugihan 1,2</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2687,13 +2353,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2722,17 +2386,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>batas ke UP2B Jawa Timur (SS Ngimbang)</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2748,13 +2406,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2861,7 +2517,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTA Jelok</t>
@@ -2882,7 +2537,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -2896,8 +2550,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2914,13 +2566,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTA Timo</t>
@@ -2941,7 +2591,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -2955,8 +2604,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2973,13 +2620,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Outlet PLTGU Tambaklorok Blok B2</t>
@@ -3000,7 +2645,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -3014,8 +2658,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3032,13 +2674,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Outlet PLTGU Tambaklorok Blok B1</t>
@@ -3059,7 +2699,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -3073,8 +2712,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3091,13 +2728,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Outlet PLTU Rembang</t>
@@ -3118,7 +2753,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -3132,8 +2766,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3150,13 +2782,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Outlet PLTA Kedungombo</t>
@@ -3177,7 +2807,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -3191,8 +2820,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3209,7 +2836,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3240,7 +2866,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -3254,8 +2879,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3272,13 +2895,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Ungaran - Tambaklorok</t>
@@ -3299,7 +2920,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -3313,8 +2933,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3331,13 +2949,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT Tambaklorok - Tanjungjati</t>
@@ -3358,7 +2974,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -3372,8 +2987,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3390,7 +3003,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3421,7 +3033,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -3435,8 +3046,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3453,7 +3062,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3484,7 +3092,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -3498,8 +3105,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3516,13 +3121,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Ungaran - Mranggen</t>
@@ -3543,7 +3146,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -3557,8 +3159,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3575,13 +3175,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>SUTT Tambaklorok - Sayung</t>
@@ -3602,7 +3200,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -3616,8 +3213,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3634,13 +3229,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Tanjungjati - Jepara</t>
@@ -3661,7 +3254,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -3675,8 +3267,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3693,7 +3283,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3724,7 +3313,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -3738,8 +3326,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3756,13 +3342,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Rembang KIT - Rembang</t>
@@ -3783,7 +3367,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -3797,8 +3380,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3815,7 +3396,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3846,7 +3426,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -3860,8 +3439,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3878,13 +3455,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT Bawen - Boyolali (arah SS Boyolali)</t>
@@ -3905,7 +3480,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -3919,8 +3493,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3937,13 +3509,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTT Ungaran - Secang</t>
@@ -3964,7 +3534,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -3978,8 +3547,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3996,13 +3563,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT Mranggen - Sambungan</t>
@@ -4023,7 +3588,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -4037,8 +3601,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4055,7 +3617,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4086,7 +3647,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -4100,8 +3660,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4118,13 +3676,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT Pati - Jekulo</t>
@@ -4145,7 +3701,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -4159,8 +3714,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4177,13 +3730,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT Rembang - Sindo</t>
@@ -4204,7 +3755,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -4218,8 +3768,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4236,7 +3784,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4267,7 +3814,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -4281,8 +3827,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4299,13 +3843,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTT Secang - Temanggung (arah SS Kesugihan)</t>
@@ -4326,7 +3868,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -4340,8 +3881,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4358,13 +3897,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>SUTT Sambungan - Purwodadi</t>
@@ -4385,7 +3922,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -4399,8 +3935,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4417,7 +3951,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4448,7 +3981,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -4462,8 +3994,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4480,7 +4010,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4511,7 +4040,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -4525,8 +4053,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4543,13 +4069,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>SUTT Purwodadi - Kedungombo</t>
@@ -4570,7 +4094,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -4584,8 +4107,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4602,7 +4123,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4633,7 +4153,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -4647,8 +4166,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4665,7 +4182,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4696,7 +4212,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -4710,8 +4225,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4728,13 +4241,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>SUTT Cepu - Bojonegoro (arah UP2B Jatim)</t>
@@ -4755,7 +4266,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -4769,8 +4279,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4787,7 +4295,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4866,12 +4373,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Tanjung Jati 1,2 total target sebesar633 MW (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 2.Pengoperasian 2 unit PLTU Rembang. Mitigasi 3.Pelaksanaan pemeliharaan pada saat beban rendah/hari libur dengan menurunkan pembebanan Komplek Pembangkitan Tanjung Jati dan mengoperasikan PLTGU Tambaklorok</t>
+          <t>1. Sudah terpasang OLS IBT Tanjung Jati 1,2 total target sebesar 633 MW (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 2. Pengoperasian 2 unit PLTU Rembang. Mitigasi 3. Pelaksanaan pemeliharaan pada saat beban rendah/hari libur dengan menurunkan pembebanan Komplek Pembangkitan Tanjung Jati dan mengoperasikan PLTGU Tambaklorok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028). 3.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028)</t>
+          <t>Jangka Pendek : 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2. Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028). 3. Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4896,17 +4403,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang skema OLS ADS Splitting Tanjungjati. 2.Pengoperasian 2 unit PLTU Rembang. 3.Pelaksanaan pemeliharaan pada saat beban rendah/hari libur dengan menurunkan pembebanan Komplek Pembangkitan Tanjung Jati dan mengoperasikan PLTGU Tambaklorok</t>
+          <t>1. Sudah terpasang skema OLS ADS Splitting Tanjungjati. 2. Pengoperasian 2 unit PLTU Rembang. 3. Pelaksanaan pemeliharaan pada saat beban rendah/hari libur dengan menurunkan pembebanan Komplek Pembangkitan Tanjung Jati dan mengoperasikan PLTGU Tambaklorok</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034,COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028). 3.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028)</t>
+          <t>Jangka Pendek : 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2. Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028). 3. Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4931,17 +4438,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan. 4.Terjadi drop tegangan di wilayah Magelang dan Yogyakarta</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan. 4. Terjadi drop tegangan di wilayah Magelang dan Yogyakarta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Pengoperasian kapasitor GI Medari dan Blora pada Sub Sistem Tanjung Jati. 2.Pengoperasian minimal 1 unit PLTGU Tambaklorok pada Sub sistem Tanjung Jati. 3.Memindahkan Trafo GI Bawen ke Subsistem Boyolali</t>
+          <t>1. Pengoperasian kapasitor GI Medari dan Blora pada Sub Sistem Tanjung Jati. 2. Pengoperasian minimal 1 unit PLTGU Tambaklorok pada Sub sistem Tanjung Jati. 3. Memindahkan Trafo GI Bawen ke Subsistem Boyolali</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan SUTT 150 kV Blora-Purwodadi (RUPTL 2025-2034,COD 2027). 3.Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028). 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung(RUPTL 2025-2034,COD 2028)</t>
+          <t>Jangka Pendek : 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2. Pembangunan SUTT 150 kV Blora-Purwodadi (RUPTL 2025-2034,COD 2027). 3. Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028). 4. Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4966,17 +4473,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.Terjadi drop tegangan di wilayah Magelang dan Yogyakarta jika IBT-3 Ungaran gangguan. 2.Komplain pelanggan KTT SINDO terkait mutu dan pelayanan tegangan saat outage PLTU Rembang 1 Unit. 3.Apabila IBT Ungaran-3 trip berpotensi tejadi kenaikan MVAR di PLTU Rembang sampai 120 MVAR</t>
+          <t>1. Terjadi drop tegangan di wilayah Magelang dan Yogyakarta jika IBT-3 Ungaran gangguan. 2. Komplain pelanggan KTT SINDO terkait mutu dan pelayanan tegangan saat outage PLTU Rembang 1 Unit. 3. Apabila IBT Ungaran-3 trip berpotensi tejadi kenaikan MVAR di PLTU Rembang sampai 120 MVAR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Pengoperasian kapasitor GI Medari pada Sub Sistem Tanjung Jati. 2.Pengoperasian minimal 1 unit PLTGU Tambaklorok pada Sub sistem Tanjung Jati. 3.Memindahkan Trafo GI Bawen ke Subsistem Boyolali</t>
+          <t>1. Pengoperasian kapasitor GI Medari pada Sub Sistem Tanjung Jati. 2. Pengoperasian minimal 1 unit PLTGU Tambaklorok pada Sub sistem Tanjung Jati. 3. Memindahkan Trafo GI Bawen ke Subsistem Boyolali</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan SUTT 150 kV Blora-Purwodadi (RUPTL 2025-2034,COD 2027). 3.Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung(RUPTL 2025-2034,COD 2028)</t>
+          <t>Jangka Pendek : 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034, COD 2026) informasi terupdate COD Desember 2027. 2.Pembangunan SUTT 150 kV Blora-Purwodadi (RUPTL 2025-2034,COD 2027). 3.Pembangunan GITET Purwodadi (RUPTL 2025- 2034,COD 2028 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028)</t>
         </is>
       </c>
     </row>
@@ -5001,17 +4508,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.Potensikehilanganpasok anpembangkitsebesar5 60 MW. 2.Komplain pelanggan karena terjadi drop tegangan saat PLTU Rembang tidak operasi. 3.Terjadi Pemadaman konsumen di ruas tersebut</t>
+          <t>1.Potensikehilangan pasok anpembangkitsebesar5 60 MW. 2. Komplain pelanggan karena terjadi drop tegangan saat PLTU Rembang tidak operasi. 3. Terjadi Pemadaman konsumen di ruas tersebut</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.Pekerjaan pemeliharaan SUTT di ruas tersebut dioptimalkan menggunakan PDKB. 2.Pekerjaan padam dilaksanakan dengan split PLTU Rembang (1# ke SS Tanjung Jati dan 1# ke SS Ngimbang). 3.Pekerjaan SUTT dijadwalkan pada periode beban rendah</t>
+          <t>1. Pekerjaan pemeliharaan SUTT di ruas tersebut dioptimalkan menggunakan PDKB. 2. Pekerjaan padam dilaksanakan dengan split PLTU Rembang (1# ke SS Tanjung Jati dan 1# ke SS Ngimbang). 3. Pekerjaan SUTT dijadwalkan pada periode beban rendah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan SUTT 150 kV Blora-Purwodadi (RUPTL 2025-2034, COD 2027). 2.PembangunanGITETPurw odadibeserta outletnya (RUPTL2023 -2032, COD2028). 3.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung(RUPTL 2025-2034,COD 2028). 4.Usulan Perubahan tower combined outlet PLTU Rembang T.3-T.70 (68 Tower) menjadi tower non- combined (UP2B akan bersurat ke UIP2B), diusulkan COD 2028</t>
+          <t>Jangka Pendek : 1. Pembangunan SUTT 150 kV Blora-Purwodadi (RUPTL 2025-2034, COD 2027). 2.Pembangunan GITETPurw odadibeserta outletnya (RUPTL 2023 -2032, COD 2028). 3. Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028). 4. Usulan Perubahan tower combined outlet PLTU Rembang T.3-T.70 (68 Tower) menjadi tower non- combined (UP2B akan bersurat ke UIP2B), diusulkan COD 2028</t>
         </is>
       </c>
     </row>
@@ -5031,22 +4538,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan Trafo di GI 150 kV Pati &gt;80% sehinggaN- 1tidakterpenuhi</t>
+          <t>[N-1] Pembebanan Trafo di GI 150 kV Pati &gt;80% sehingga N- 1 tidakterpenuhi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.Terjadi Drop tegangan di sisi 20 kV jika beban dipasok dari GI lain saat terjadi gangguan di trafo GI 150 kV Pati. 2.Terdapat potensi padam 15 MW pada saat dilakukan pemeliharaan 1 trafo. 3.Potensi pertumbuhan beban terhambat di GI Pati</t>
+          <t>1. Terjadi Drop tegangan di sisi 20 kV jika beban dipasok dari GI lain saat terjadi gangguan di trafo GI 150 kV Pati. 2. Terdapat potensi padam 15 MW pada saat dilakukan pemeliharaan 1 trafo. 3. Potensi pertumbuhan beban terhambat di GI Pati</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pekerjaanpemeliha raandilaksanakanp adasaatbebanren dah/harilibur</t>
+          <t>Pekerjaanpemeliha raandilaksanakanp ada saat beban ren dah/hari libur</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Penambahan Trafo ke-4 GI 150 kV Pati (RUPTL 2025- 2034, COD2025) update proses pengadaan. 2.Pembangunan GI 150 kV Pati II (Trangkil) RUPTL 2025-2034, COD 2025) update : kontrak COD Semester 1 2026, terkendala kinerja vendor pelaksana</t>
+          <t>Jangka Pendek : 1. Penambahan Trafo ke-4 GI 150 kV Pati (RUPTL 2025- 2034, COD 2025) update proses pengadaan. 2. Pembangunan GI 150 kV Pati II (Trangkil) RUPTL 2025-2034, COD 2025) update : kontrak COD Semester 1 2026, terkendala kinerja vendor pelaksana</t>
         </is>
       </c>
     </row>
@@ -5071,17 +4578,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.Berpotensi padam ±30 MW pada saat terjadi pemeliharaan padam menginap atau gangguan trafo. 2.Terjadi Drop tegangan di sisi 20 kV bila dilakukan manuver pemindahan beban apabila terjadi gangguan di trafo GI 150 kV Kudus. 3.Potensi pertumbuhan beban terhambat di GI 150 kV Kudus</t>
+          <t>1. Berpotensi padam ±30 MW pada saat terjadi pemeliharaan padam menginap atau gangguan trafo. 2. Terjadi Drop tegangan di sisi 20 kV bila dilakukan manuver pemindahan beban apabila terjadi gangguan di trafo GI 150 kV Kudus. 3. Potensi pertumbuhan beban terhambat di GI 150 kV Kudus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.Pembatasan pembebanan trafo di GI 150 kV Kudus. 2.Pengoperasian trafo mobile di GI 150 kV Kudus</t>
+          <t>1. Pembatasan pembebanan trafo di GI 150 kV Kudus. 2. Pengoperasian trafo mobile di GI 150 kV Kudus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan ekstension Trafo-4 GI 150 kV Kudus (RUPTL 2025-2034, COD 2025). Update rencana COD Juli 2026 2.Percepatan pembangunan GI 150 kV Kudus II/ Nalumsari (RUPTL 2025- 2034, COD 2025). Update : sudah terkontrak, estimasi COD SMT-2 2026, terkendala kinerja vendor pelaksana</t>
+          <t>Jangka Pendek : 1. Pembangunan ekstension Trafo-4 GI 150 kV Kudus (RUPTL 2025-2034, COD 2025). Update rencana COD Juli 2026 2. Percepatan pembangunan GI 150 kV Kudus II/ Nalumsari (RUPTL 2025- 2034, COD 2025). Update : sudah terkontrak, estimasi COD SMT-2 2026, terkendala kinerja vendor pelaksana</t>
         </is>
       </c>
     </row>
@@ -5106,7 +4613,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.Terdapat komplain pelanggan terkait Tingkat Mutu Pelayanan. 2.Proses sinkron PLTU Rembang mengalami kesulitan</t>
+          <t>1. Terdapat komplain pelanggan terkait Tingkat Mutu Pelayanan. 2. Proses sinkron PLTU Rembang mengalami kesulitan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5116,7 +4623,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pemasangan Defense Scheme UVLS di GI Blora, Estimasi S1Tahun 2026. 2.PercepatanPembangunan SUTT 150 kVBlora- Purwodadi(RUPTL 2025- 2034, COD2027). 3.Percepatanpembangunan GITETPurwodadibeserta outletnya (RUPTL 2025- 2034,COD2028). 4.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung(RUPTL 2025-2034,COD 2028)</t>
+          <t>Jangka Pendek : 1. Pemasangan Defense Scheme UVLS di GI Blora, Estimasi S1 Tahun 2026. 2. PercepatanPembangunan SUTT 150 kV Blora- Purwodadi (RUPTL 2025- 2034, COD 2027). 3. Percepatanpembangunan GITET Purwodadi beserta outletnya (RUPTL 2025- 2034,COD 2028). 4. Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028)</t>
         </is>
       </c>
     </row>
@@ -5141,7 +4648,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.GI Medari padam sebesar53 MW saat ada pekerjaan bay SUTT di GI tersebut &amp; sirkit lain gangguan. Dampak 2.Fleksibilitas operasi dan keandalan berkurang</t>
+          <t>1. GI Medari padam sebesar 53 MW saat ada pekerjaan bay SUTT di GI tersebut &amp; sirkit lain gangguan. Dampak 2. Fleksibilitas operasi dan keandalan berkurang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5176,12 +4683,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Berpotensi padam 257 MW jika terjadi padam pada GI Medari, Gejayan, dan Kentungan Trafo 3&amp;4. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Berpotensi padam 257 MW jika terjadi padam pada GI Medari, Gejayan, dan Kentungan Trafo 3&amp;4. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Kentungan- Sanggrahan &amp; Medari- Sanggrahan sebesar 197MW. (Realis asi BP Tahun 2025, 14 Oktober 2025-5721MW). 2.Saat pekerjaan SUTT Sanggrahan- Medari- Kentungan, dilakukan rekonfigurasi GI Gejayan dipasok SS Pedan 3,4 (GI Medari radial satu penghantar)</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Kentungan- Sanggrahan &amp; Medari- Sanggrahan sebesar 197 MW. (Realis asi BP Tahun 2025, 14 Oktober 2025 -5721MW). 2. Saat pekerjaan SUTT Sanggrahan- Medari- Kentungan, dilakukan rekonfigurasi GI Gejayan dipasok SS Pedan 3,4 (GI Medari radial satu penghantar)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5211,12 +4718,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Berpotensi padam 257 MW jika terjadi padam pada GI Medari, Gejayan, dan Kentungan Trafo 3&amp;4. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Berpotensi padam 257 MW jika terjadi padam pada GI Medari, Gejayan, dan Kentungan Trafo 3&amp;4. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Kentungan- Sanggrahan &amp; Medari- Sanggrahan sebesar 197MW. (Realis asiBPTahun202 5, 14 Oktober 2025-5721MW). 2.Saat pekerjaan SUTT Sanggrahan- Medari- Kentungan, dilakukan rekonfigurasi GI Gejayan dipasok SS Pedan 3,4 (GI Medari radial satu penghantar)</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Kentungan- Sanggrahan &amp; Medari- Sanggrahan sebesar 197 MW. (Realis asi BPTahun202 5, 14 Oktober 2025 -5721MW). 2. Saat pekerjaan SUTT Sanggrahan- Medari- Kentungan, dilakukan rekonfigurasi GI Gejayan dipasok SS Pedan 3,4 (GI Medari radial satu penghantar)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5246,12 +4753,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Berpotensi padam 247 MW jika terjadi padam pada GI Medari, Gejayan, Dampak dan Kentungan Trafo 3&amp;4. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Berpotensi padam 247 MW jika terjadi padam pada GI Medari, Gejayan, Dampak dan Kentungan Trafo 3&amp;4. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Kentungan- Sanggrahan &amp; Medari- Sanggrahan sebesar Mitigasi 197MW. (Realis asiBPTahun202 5, 14 Oktober 2025-5721MW) 2.Saat pekerjaan SUTT Sanggrahan- Medari- Kentungan, dilakukan rekonfigurasi GI Gejayan dipasok SS Pedan 3,4 (GI Medari radial satu penghantar)</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Kentungan- Sanggrahan &amp; Medari- Sanggrahan sebesar Mitigasi 197 MW. (Realis asi BPTahun202 5, 14 Oktober 2025 -5721MW) 2. Saat pekerjaan SUTT Sanggrahan- Medari- Kentungan, dilakukan rekonfigurasi GI Gejayan dipasok SS Pedan 3,4 (GI Medari radial satu penghantar)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5281,12 +4788,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Berpotensi padam 229 MW jika terjadi padam pada GI Bringin, Boyolali, Mojosongo dan Banyudono. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Berpotensi padam 229 MW jika terjadi padam pada GI Bringin, Boyolali, Mojosongo dan Banyudono. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Jelok-Ungaran sebesar 91MW. (Realisas iBPTahun2025, 14 Oktober 2025 -5721MW) 2.Saat pekerjaan SUTT Jelok- Ungaran, dilakukan rekonfigurasi GI Jelok dipasok SS Boyolali</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Jelok-Ungaran sebesar 91 MW. (Realisas iBPTahun2025, 14 Oktober 2025 -5721 MW) 2. Saat pekerjaan SUTT Jelok- Ungaran, dilakukan rekonfigurasi GI Jelok dipasok SS Boyolali</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5321,12 +4828,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Ungaran-Bawen sebesar 256MW. (Realis asiBPTahun202 5, 14 Oktober 2025-5721MW) 2.Saat pekerjaan SUTT Jelok- Ungaran, dilakukan rekonfigurasi GI Kentungan dipasok SS Pedan 3,4</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Ungaran-Bawen sebesar 256 MW. (Realis asi BPTahun202 5, 14 Oktober 2025 -5721MW) 2. Saat pekerjaan SUTT Jelok- Ungaran, dilakukan rekonfigurasi GI Kentungan dipasok SS Pedan 3,4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jangka Menengah: 1.Rekonduktoring SUTT 150 kV Sanggrahan-Medari menjadi HTLSC 1250 A per sirkit. (RUPTL 2025-2034, COD 2028), Update: sudah terkontrak estimasi COD 2026. 2.Rekonduktoring SUTT 150 kV Sanggrahan-Kentungan menjadi HTLSC 1250 A per sirkit. Update : sudah terkontrak Estimasi COD 2026. Belum ada di RUPTL. Jangka Menengah : 3.Rekonduktoring SUTT 150 kV Medari-Kentungan menjadi HTLSC 1250 A per sirkit. (RUPTL 2025-2034, COD 2029). Update: Info UIT rencana terkontrak 2026,estimasiCOD 2027</t>
+          <t>Jangka Menengah: 1. Rekonduktoring SUTT 150 kV Sanggrahan-Medari menjadi HTLSC 1250 A per sirkit. (RUPTL 2025-2034, COD 2028), Update: sudah terkontrak estimasi COD 2026. 2. Rekonduktoring SUTT 150 kV Sanggrahan-Kentungan menjadi HTLSC 1250 A per sirkit. Update : sudah terkontrak Estimasi COD 2026. Belum ada di RUPTL. Jangka Menengah : 3. Rekonduktoring SUTT 150 kV Medari-Kentungan menjadi HTLSC 1250 A per sirkit. (RUPTL 2025-2034, COD 2029). Update: Info UIT rencana terkontrak 2026,estimasi COD 2027</t>
         </is>
       </c>
     </row>
